--- a/src/test/resources/ruleservice_repo/TestWebservicesDeployUI/someDeployment/Hello_Rule/Corporate Rating.xlsx
+++ b/src/test/resources/ruleservice_repo/TestWebservicesDeployUI/someDeployment/Hello_Rule/Corporate Rating.xlsx
@@ -1110,25 +1110,25 @@
     <t>&lt; 100</t>
   </si>
   <si>
-    <t>&lt; 21K</t>
-  </si>
-  <si>
-    <t>&gt;= 80K</t>
+    <t>&lt; 21000</t>
+  </si>
+  <si>
+    <t>&gt;= 80000</t>
   </si>
   <si>
     <t>//currency = EUR</t>
   </si>
   <si>
-    <t>[50K .. 80K)</t>
-  </si>
-  <si>
-    <t>[5K .. 50K)</t>
-  </si>
-  <si>
-    <t>&gt; 52.5K</t>
-  </si>
-  <si>
-    <t>[21K .. 52.5K]</t>
+    <t>[50000 .. 80000)</t>
+  </si>
+  <si>
+    <t>[5000 .. 50000)</t>
+  </si>
+  <si>
+    <t>&gt; 52500</t>
+  </si>
+  <si>
+    <t>[21000 .. 52500]</t>
   </si>
   <si>
     <t>Tests for "Risk of Profile"</t>
